--- a/EIANN/data/supplementary_tables/Table_S8_fmnist_hyperparams.xlsx
+++ b/EIANN/data/supplementary_tables/Table_S8_fmnist_hyperparams.xlsx
@@ -465,7 +465,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Winit (H1)</t>
+          <t>W_init (H1)</t>
         </is>
       </c>
       <c r="B2" t="n">
@@ -515,7 +515,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Winit (H2)</t>
+          <t>W_init (H2)</t>
         </is>
       </c>
       <c r="B4" t="n">
@@ -565,7 +565,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Winit (Output)</t>
+          <t>W_init (Output)</t>
         </is>
       </c>
       <c r="B6" t="n">
@@ -609,7 +609,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H1)</t>
+          <t>Y_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -637,7 +637,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H1)</t>
+          <t>W_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -665,7 +665,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H1)</t>
+          <t>Q_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -693,7 +693,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H1)</t>
+          <t>R_init (SomaI, H1)</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -721,7 +721,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, H2)</t>
+          <t>Y_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -749,7 +749,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Winit (SomaI, H2)</t>
+          <t>W_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -777,7 +777,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, H2)</t>
+          <t>Q_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -805,7 +805,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, H2)</t>
+          <t>R_init (SomaI, H2)</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -833,7 +833,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Yinit (SomaI, Output)</t>
+          <t>Y_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -861,7 +861,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Winit (SomaI, Output)</t>
+          <t>W_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -889,7 +889,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Qinit (SomaI, Output)</t>
+          <t>Q_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -917,7 +917,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Rinit (SomaI, Output)</t>
+          <t>R_init (SomaI, Output)</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -945,7 +945,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H1)</t>
+          <t>Y_init (DendI, H1)</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1005,7 +1005,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Bscale (H1)</t>
+          <t>B_scale (H1)</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -1065,7 +1065,7 @@
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H1)</t>
+          <t>Q_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
@@ -1125,7 +1125,7 @@
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H1)</t>
+          <t>R_sum (DendI, H1)</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
@@ -1155,7 +1155,7 @@
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Yinit (DendI, H2)</t>
+          <t>Y_init (DendI, H2)</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
@@ -1215,7 +1215,7 @@
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Bscale (H2)</t>
+          <t>B_scale (H2)</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
@@ -1275,7 +1275,7 @@
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Qsum (DendI, H2)</t>
+          <t>Q_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
@@ -1335,7 +1335,7 @@
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Rsum (DendI, H2)</t>
+          <t>R_sum (DendI, H2)</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
